--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487836_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487836_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4665</v>
+        <v>7.4627</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0632</v>
+        <v>7.2356</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4033</v>
+        <v>0.2272</v>
       </c>
       <c r="G2" t="n">
         <v>3.9501</v>
@@ -610,13 +610,13 @@
         <v>1.0406</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4945</v>
+        <v>0.4908</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1396</v>
+        <v>0.312</v>
       </c>
       <c r="U2" t="n">
-        <v>0.355</v>
+        <v>0.1788</v>
       </c>
       <c r="V2" t="n">
         <v>1.9813</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8231</v>
+        <v>5.0258</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9217</v>
+        <v>4.6235</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9014</v>
+        <v>0.4023</v>
       </c>
       <c r="G3" t="n">
         <v>4.022</v>
@@ -688,13 +688,13 @@
         <v>1.0406</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6741</v>
+        <v>0.8769</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8416</v>
+        <v>0.5434</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8326</v>
+        <v>0.3334</v>
       </c>
       <c r="V3" t="n">
         <v>1.1675</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1954</v>
+        <v>3.017</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1263</v>
+        <v>2.9772</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0398</v>
       </c>
       <c r="G4" t="n">
         <v>-0.5361</v>
@@ -766,13 +766,13 @@
         <v>0.8325</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2539</v>
+        <v>1.0755</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.7577</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3471</v>
+        <v>0.3178</v>
       </c>
       <c r="V4" t="n">
         <v>1.6452</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7385</v>
+        <v>2.7759</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6239</v>
+        <v>2.3677</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1146</v>
+        <v>0.4082</v>
       </c>
       <c r="G5" t="n">
         <v>0.3762</v>
@@ -844,13 +844,13 @@
         <v>0.6244</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5434</v>
+        <v>0.5808</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7358</v>
+        <v>0.4796</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1924</v>
+        <v>0.1012</v>
       </c>
       <c r="V5" t="n">
         <v>4.3163</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. ORDOÑEZ OCHOA</t>
+          <t>P. MARIN FONTAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6857</v>
+        <v>2.3368</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0738</v>
+        <v>3.5627</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3881</v>
+        <v>-1.226</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5765</v>
+        <v>0.2153</v>
       </c>
       <c r="H6" t="n">
-        <v>2.761</v>
+        <v>2.467</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.3375</v>
+        <v>-2.2517</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5952</v>
+        <v>1.4605</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5816</v>
+        <v>2.859</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.9864</v>
+        <v>-1.3985</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1717</v>
+        <v>-1.2452</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1794</v>
+        <v>-0.3921</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3512</v>
+        <v>-0.8532</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6244</v>
+        <v>1.0406</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6244</v>
+        <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9479</v>
+        <v>0.2672</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7887</v>
+        <v>0.121</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1592</v>
+        <v>0.1462</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6899</v>
+        <v>0.8137</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6899</v>
+        <v>1.9813</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. MARIN FONTAN</t>
+          <t>I. ORDOÑEZ OCHOA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6286</v>
+        <v>1.5469</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8546</v>
+        <v>1.8176</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.226</v>
+        <v>-0.2707</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2153</v>
+        <v>-0.5765</v>
       </c>
       <c r="H7" t="n">
-        <v>2.467</v>
+        <v>2.761</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.2517</v>
+        <v>-3.3375</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4605</v>
+        <v>0.5952</v>
       </c>
       <c r="K7" t="n">
-        <v>2.859</v>
+        <v>2.5816</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3985</v>
+        <v>-1.9864</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2452</v>
+        <v>-1.1717</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3921</v>
+        <v>0.1794</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8532</v>
+        <v>-1.3512</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0406</v>
+        <v>0.6244</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0406</v>
+        <v>0.6244</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.441</v>
+        <v>0.8091</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5872000000000001</v>
+        <v>0.5325</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1462</v>
+        <v>0.2767</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8137</v>
+        <v>0.6899</v>
       </c>
       <c r="W7" t="n">
-        <v>1.9813</v>
+        <v>0.6899</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7088</v>
+        <v>0.2009</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1228</v>
+        <v>1.9085</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.414</v>
+        <v>-1.7076</v>
       </c>
       <c r="G8" t="n">
         <v>0.1991</v>
@@ -1078,13 +1078,13 @@
         <v>0.4162</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6772</v>
+        <v>0.1693</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2824</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3948</v>
+        <v>0.1012</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5838</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1</v>
+        <v>-0.2354</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1254</v>
+        <v>0.6845</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1255</v>
+        <v>-0.9199000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>0.0057</v>
@@ -1156,13 +1156,13 @@
         <v>1.2487</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0463</v>
+        <v>0.7183</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0033</v>
+        <v>0.5558</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.043</v>
+        <v>0.1625</v>
       </c>
       <c r="V9" t="n">
         <v>-1.1675</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. HANSEN GUTIERREZ</t>
+          <t>J. GARCIA-ABRIL GUERRERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5887</v>
+        <v>-1.2667</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5592</v>
+        <v>-1.4576</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0294</v>
+        <v>0.1909</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4778</v>
+        <v>-0.946</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1919</v>
+        <v>-0.955</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2859</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4287</v>
+        <v>-0.5784</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.0576</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4287</v>
+        <v>-0.636</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.049</v>
+        <v>-0.3676</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1919</v>
+        <v>-1.0126</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1429</v>
+        <v>0.645</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.4162</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1109</v>
+        <v>0.0737</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1305</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0196</v>
+        <v>0.1423</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. GARCIA-ABRIL GUERRERO</t>
+          <t>I. HANSEN GUTIERREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8421</v>
+        <v>-1.4522</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8862</v>
+        <v>-1.4521</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0441</v>
+        <v>-0.0001</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.946</v>
+        <v>-1.4778</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.955</v>
+        <v>-0.1919</v>
       </c>
       <c r="I11" t="n">
-        <v>0.008999999999999999</v>
+        <v>-1.2859</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5784</v>
+        <v>-1.4287</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0576</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.636</v>
+        <v>-1.4287</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3676</v>
+        <v>-0.049</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0126</v>
+        <v>-0.1919</v>
       </c>
       <c r="O11" t="n">
-        <v>0.645</v>
+        <v>0.1429</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6244</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4162</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5017</v>
+        <v>0.0256</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4972</v>
+        <v>-0.0233</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0045</v>
+        <v>0.0489</v>
       </c>
       <c r="V11" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1973</v>
+        <v>-2.8193</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7013</v>
+        <v>-2.5289</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4959</v>
+        <v>-0.2904</v>
       </c>
       <c r="G12" t="n">
         <v>-2.5142</v>
@@ -1390,13 +1390,13 @@
         <v>0.2081</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8912</v>
+        <v>-0.5133</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3791</v>
+        <v>-0.2067</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5121</v>
+        <v>-0.3066</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.3328</v>
+        <v>-3.6543</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.5885</v>
+        <v>-1.9099</v>
       </c>
       <c r="F13" t="n">
         <v>-1.7444</v>
@@ -1468,10 +1468,10 @@
         <v>0.8325</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0125</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7887</v>
+        <v>0.4672</v>
       </c>
       <c r="U13" t="n">
         <v>0.2238</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12.2857</v>
+        <v>12.9381</v>
       </c>
       <c r="E14" t="n">
-        <v>17.1765</v>
+        <v>17.8288</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.8908</v>
+        <v>-4.890700000000001</v>
       </c>
       <c r="G14" t="n">
         <v>-2.0001</v>
@@ -1546,13 +1546,13 @@
         <v>8.3248</v>
       </c>
       <c r="S14" t="n">
-        <v>4.612399999999999</v>
+        <v>5.264899999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8863</v>
+        <v>3.5388</v>
       </c>
       <c r="U14" t="n">
-        <v>1.7263</v>
+        <v>1.7262</v>
       </c>
       <c r="V14" t="n">
         <v>8.632700000000002</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>W. LEVEQUE</t>
+          <t>L. GARCIA PEREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5734</v>
+        <v>2.0994</v>
       </c>
       <c r="E15" t="n">
-        <v>6.1447</v>
+        <v>0.4703</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.5712</v>
+        <v>1.6291</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8396</v>
+        <v>1.4145</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4714</v>
+        <v>0.1172</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3682</v>
+        <v>1.2973</v>
       </c>
       <c r="J15" t="n">
-        <v>5.5057</v>
+        <v>0.3818</v>
       </c>
       <c r="K15" t="n">
-        <v>4.6435</v>
+        <v>0.2642</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8621</v>
+        <v>0.1176</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.6661</v>
+        <v>1.0327</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.1722</v>
+        <v>-0.147</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4939</v>
+        <v>1.1797</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.4568</v>
+        <v>0.8325</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6506</v>
+        <v>0.0824</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5526</v>
+        <v>-0.1414</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0979</v>
+        <v>0.2238</v>
       </c>
       <c r="V15" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X15" t="n">
         <v>-0.4599</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.1675</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-1.6275</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. GARCIA PEREZ</t>
+          <t>N. MARINA PARRA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7065</v>
+        <v>1.6297</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3632</v>
+        <v>1.4914</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3433</v>
+        <v>0.1383</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4145</v>
+        <v>1.6483</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1172</v>
+        <v>-0.8018</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2973</v>
+        <v>2.4501</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3818</v>
+        <v>1.4729</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2642</v>
+        <v>-0.369</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1176</v>
+        <v>1.8418</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0327</v>
+        <v>0.1755</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.147</v>
+        <v>-0.4328</v>
       </c>
       <c r="O16" t="n">
-        <v>1.1797</v>
+        <v>0.6082</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8325</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8325</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3105</v>
+        <v>-0.0186</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2486</v>
+        <v>0.0186</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0619</v>
+        <v>-0.0372</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. MARINA PARRA</t>
+          <t>W. LEVEQUE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4154</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2771</v>
+        <v>4.7516</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1383</v>
+        <v>-3.9235</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6483</v>
+        <v>2.8396</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8018</v>
+        <v>2.4714</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4501</v>
+        <v>0.3682</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4729</v>
+        <v>5.5057</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.369</v>
+        <v>4.6435</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8418</v>
+        <v>0.8621</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1755</v>
+        <v>-2.6661</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4328</v>
+        <v>-2.1722</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6082</v>
+        <v>-0.4939</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.6244</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2329</v>
+        <v>-0.0948</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1957</v>
+        <v>0.1596</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0372</v>
+        <v>-0.2544</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.4599</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.6275</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9565</v>
+        <v>0.5064</v>
       </c>
       <c r="E18" t="n">
-        <v>4.7596</v>
+        <v>3.9023</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.8031</v>
+        <v>-3.396</v>
       </c>
       <c r="G18" t="n">
         <v>3.0448</v>
@@ -1858,13 +1858,13 @@
         <v>0.6244</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0477</v>
+        <v>-0.4978</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7763</v>
+        <v>-0.0809</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.824</v>
+        <v>-0.4169</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5838</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8345</v>
+        <v>-0.5551</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0537</v>
+        <v>0.0534</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7806999999999999</v>
+        <v>-0.6085</v>
       </c>
       <c r="G19" t="n">
         <v>-0.854</v>
@@ -1936,13 +1936,13 @@
         <v>0.4162</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3967</v>
+        <v>-0.1173</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1305</v>
+        <v>-0.0233</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2662</v>
+        <v>-0.0939</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.091</v>
+        <v>-0.9965000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7648</v>
+        <v>-0.8719</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3262</v>
+        <v>-0.1246</v>
       </c>
       <c r="G20" t="n">
         <v>-2.0244</v>
@@ -2014,13 +2014,13 @@
         <v>0.2081</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1416</v>
+        <v>0.236</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1396</v>
+        <v>0.0324</v>
       </c>
       <c r="U20" t="n">
-        <v>0.002</v>
+        <v>0.2036</v>
       </c>
       <c r="V20" t="n">
         <v>0.5838</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0836</v>
+        <v>-1.859</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0145</v>
+        <v>0.0926</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.069</v>
+        <v>-1.9516</v>
       </c>
       <c r="G21" t="n">
         <v>0.0057</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3379</v>
+        <v>-0.1134</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1305</v>
+        <v>-0.0233</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2075</v>
+        <v>-0.09</v>
       </c>
       <c r="V21" t="n">
         <v>-1.7513</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. STRIKKER</t>
+          <t>A. LAFUENTE SISO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9157</v>
+        <v>-2.5209</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5516</v>
+        <v>0.0769</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.364</v>
+        <v>-2.5979</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4148</v>
+        <v>-1.1643</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7119</v>
+        <v>-2.3244</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7029</v>
+        <v>1.1601</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0388</v>
+        <v>1.2487</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2583</v>
+        <v>-0.1564</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7805</v>
+        <v>1.405</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3761</v>
+        <v>-2.4129</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4536</v>
+        <v>-2.168</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0776</v>
+        <v>-0.2449</v>
       </c>
       <c r="P22" t="n">
-        <v>1.0406</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0406</v>
+        <v>1.2487</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4978</v>
+        <v>-0.5242</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5129</v>
+        <v>-0.2581</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0151</v>
+        <v>-0.2661</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0437</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0437</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. MAZAIRA GOMEZ</t>
+          <t>M. STRIKKER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3947</v>
+        <v>-2.7386</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2888</v>
+        <v>-1.3373</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1058</v>
+        <v>-1.4012</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9643</v>
+        <v>-2.4148</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.0918</v>
+        <v>-1.7119</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1275</v>
+        <v>-0.7029</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9261</v>
+        <v>-1.0388</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0176</v>
+        <v>-0.2583</v>
       </c>
       <c r="L23" t="n">
-        <v>0.9438</v>
+        <v>-0.7805</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8904</v>
+        <v>-1.3761</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.0741</v>
+        <v>-1.4536</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1837</v>
+        <v>0.0776</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2081</v>
+        <v>1.0406</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4085</v>
+        <v>-0.3206</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1744</v>
+        <v>-0.2985</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2341</v>
+        <v>-0.0221</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.8137</v>
+        <v>-1.0437</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.8137</v>
+        <v>-1.0437</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. LAFUENTE SISO</t>
+          <t>A. MAZAIRA GOMEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.5123</v>
+        <v>-2.8985</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5659999999999999</v>
+        <v>-0.6459</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.9463</v>
+        <v>-2.2526</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.1643</v>
+        <v>-0.9643</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.3244</v>
+        <v>-2.0918</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1601</v>
+        <v>1.1275</v>
       </c>
       <c r="J24" t="n">
-        <v>1.2487</v>
+        <v>0.9261</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1564</v>
+        <v>-0.0176</v>
       </c>
       <c r="L24" t="n">
-        <v>1.405</v>
+        <v>0.9438</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.4129</v>
+        <v>-1.8904</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.168</v>
+        <v>-2.0741</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2449</v>
+        <v>0.1837</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.8325</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5155</v>
+        <v>-0.9124</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.901</v>
+        <v>-0.5314</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6145</v>
+        <v>-0.3809</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.8137</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.1675</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.1059</v>
+        <v>-4.3519</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.4143</v>
+        <v>-3.0928</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6917</v>
+        <v>-1.2591</v>
       </c>
       <c r="G25" t="n">
         <v>0.469</v>
@@ -2404,13 +2404,13 @@
         <v>1.4568</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.6571</v>
+        <v>-0.9031</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.901</v>
+        <v>-0.5795</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7561</v>
+        <v>-0.3235</v>
       </c>
       <c r="V25" t="n">
         <v>-4.334</v>
@@ -2437,28 +2437,28 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-12.2859</v>
+        <v>-10.8569</v>
       </c>
       <c r="E26" t="n">
-        <v>4.890899999999999</v>
+        <v>4.890600000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-17.1764</v>
+        <v>-15.7476</v>
       </c>
       <c r="G26" t="n">
-        <v>2.000100000000001</v>
+        <v>2.000099999999998</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.3476</v>
+        <v>-3.347599999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>5.3476</v>
+        <v>5.347599999999999</v>
       </c>
       <c r="J26" t="n">
         <v>11.3505</v>
       </c>
       <c r="K26" t="n">
-        <v>8.0032</v>
+        <v>8.003199999999998</v>
       </c>
       <c r="L26" t="n">
         <v>3.3473</v>
@@ -2482,13 +2482,13 @@
         <v>7.284199999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.6124</v>
+        <v>-3.1838</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.7261</v>
+        <v>-1.7258</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.8865</v>
+        <v>-1.4576</v>
       </c>
       <c r="V26" t="n">
         <v>-8.6326</v>
